--- a/FSDL Problem Statements.xlsx
+++ b/FSDL Problem Statements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashish Patil\Desktop\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF2E5458-F561-419F-87F7-21FBAC4699D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F1420F0-8628-4D15-A685-3DA2C665ECD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
